--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 4.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 4.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Keuangan 4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Keuangan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7035D026-141C-4E4C-89C8-84A483DCE408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0D1C1107-655D-49B5-8DC2-E16431969AA2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -165,7 +164,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -424,9 +423,30 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -435,27 +455,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -502,7 +501,7 @@
         <xdr:cNvPr id="1025" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{904681E3-1995-F772-64A1-EE1D24D58567}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{904681E3-1995-F772-64A1-EE1D24D58567}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -993,7 +992,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6971900-5A9D-4DF3-B648-15733AA91051}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -1020,49 +1019,49 @@
       </c>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="17" t="s">
         <v>17</v>
       </c>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
@@ -1072,13 +1071,34 @@
       <c r="C4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="16"/>
+      <c r="D4" s="13" t="str">
+        <f>VLOOKUP(LEFT(B4,2),$B$15:$D$18,2,FALSE)</f>
+        <v>Bandung Selatan</v>
+      </c>
+      <c r="E4" s="13" t="str">
+        <f>HLOOKUP(MID(B4,3,1),$B$21:$E$23,2,FALSE)</f>
+        <v>Podomoro</v>
+      </c>
+      <c r="F4" s="14">
+        <f>VLOOKUP(LEFT(B4,2),$B$15:$D$18,3,FALSE)</f>
+        <v>1000000000</v>
+      </c>
+      <c r="G4" s="15" t="str">
+        <f>RIGHT(B4,1)</f>
+        <v>5</v>
+      </c>
+      <c r="H4" s="13">
+        <f>F4*G4</f>
+        <v>5000000000</v>
+      </c>
+      <c r="I4" s="14">
+        <f>HLOOKUP(E4,$C$22:$E$23,2,FALSE)</f>
+        <v>50000000</v>
+      </c>
+      <c r="J4" s="16">
+        <f>IF(G4&gt;5,H4*0.02,0)</f>
+        <v>100000000</v>
+      </c>
       <c r="K4" s="13"/>
       <c r="L4" s="2"/>
     </row>
@@ -1089,12 +1109,30 @@
       <c r="C5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="14"/>
+      <c r="D5" s="13" t="str">
+        <f t="shared" ref="D5:D8" si="0">VLOOKUP(LEFT(B5,2),$B$15:$D$18,2,FALSE)</f>
+        <v>Bandung Utara</v>
+      </c>
+      <c r="E5" s="13" t="str">
+        <f t="shared" ref="E5:E8" si="1">HLOOKUP(MID(B5,3,1),$B$21:$E$23,2,FALSE)</f>
+        <v>Waskita</v>
+      </c>
+      <c r="F5" s="14">
+        <f t="shared" ref="F5:F8" si="2">VLOOKUP(LEFT(B5,2),$B$15:$D$18,3,FALSE)</f>
+        <v>750000000</v>
+      </c>
+      <c r="G5" s="15" t="str">
+        <f t="shared" ref="G5:G8" si="3">RIGHT(B5,1)</f>
+        <v>2</v>
+      </c>
+      <c r="H5" s="13">
+        <f t="shared" ref="H5:H8" si="4">F5*G5</f>
+        <v>1500000000</v>
+      </c>
+      <c r="I5" s="14">
+        <f t="shared" ref="I5:I8" si="5">HLOOKUP(E5,$C$22:$E$23,2,FALSE)</f>
+        <v>45000000</v>
+      </c>
       <c r="J5" s="16"/>
       <c r="K5" s="13"/>
       <c r="L5" s="2"/>
@@ -1106,12 +1144,30 @@
       <c r="C6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
+      <c r="D6" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Bandung Timur</v>
+      </c>
+      <c r="E6" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Ciputra</v>
+      </c>
+      <c r="F6" s="14">
+        <f t="shared" si="2"/>
+        <v>850000000</v>
+      </c>
+      <c r="G6" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="H6" s="13">
+        <f t="shared" si="4"/>
+        <v>2550000000</v>
+      </c>
+      <c r="I6" s="14">
+        <f t="shared" si="5"/>
+        <v>40000000</v>
+      </c>
       <c r="J6" s="16"/>
       <c r="K6" s="13"/>
       <c r="L6" s="2"/>
@@ -1123,12 +1179,30 @@
       <c r="C7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
+      <c r="D7" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Bandung Selatan</v>
+      </c>
+      <c r="E7" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Podomoro</v>
+      </c>
+      <c r="F7" s="14">
+        <f t="shared" si="2"/>
+        <v>1000000000</v>
+      </c>
+      <c r="G7" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H7" s="13">
+        <f t="shared" si="4"/>
+        <v>1000000000</v>
+      </c>
+      <c r="I7" s="14">
+        <f t="shared" si="5"/>
+        <v>50000000</v>
+      </c>
       <c r="J7" s="16"/>
       <c r="K7" s="13"/>
       <c r="L7" s="2"/>
@@ -1140,66 +1214,84 @@
       <c r="C8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="14"/>
+      <c r="D8" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>Bandung Utara</v>
+      </c>
+      <c r="E8" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Waskita</v>
+      </c>
+      <c r="F8" s="14">
+        <f t="shared" si="2"/>
+        <v>750000000</v>
+      </c>
+      <c r="G8" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H8" s="13">
+        <f t="shared" si="4"/>
+        <v>750000000</v>
+      </c>
+      <c r="I8" s="14">
+        <f t="shared" si="5"/>
+        <v>45000000</v>
+      </c>
       <c r="J8" s="16"/>
       <c r="K8" s="13"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="25" t="s">
+      <c r="C10" s="26"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="24"/>
-      <c r="J10" s="27" t="s">
+      <c r="I10" s="22"/>
+      <c r="J10" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="K10" s="26"/>
+      <c r="K10" s="24"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="2:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
@@ -1310,12 +1402,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E9:G9"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="K2:K3"/>
@@ -1323,16 +1416,15 @@
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="J10:K10"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J10" r:id="rId1" xr:uid="{A38C7E0C-6A8B-4E2C-AB0A-B862BC909F0D}"/>
+    <hyperlink ref="J10" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 4.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 4.xlsx
@@ -1,28 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Keuangan\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB54951-5801-4038-9AD8-8F471EF704A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{0D1C1107-655D-49B5-8DC2-E16431969AA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
@@ -164,7 +196,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -501,7 +533,7 @@
         <xdr:cNvPr id="1025" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{904681E3-1995-F772-64A1-EE1D24D58567}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{904681E3-1995-F772-64A1-EE1D24D58567}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -992,7 +1024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6971900-5A9D-4DF3-B648-15733AA91051}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -1079,12 +1111,12 @@
         <f>HLOOKUP(MID(B4,3,1),$B$21:$E$23,2,FALSE)</f>
         <v>Podomoro</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="13">
         <f>VLOOKUP(LEFT(B4,2),$B$15:$D$18,3,FALSE)</f>
         <v>1000000000</v>
       </c>
-      <c r="G4" s="15" t="str">
-        <f>RIGHT(B4,1)</f>
+      <c r="G4" s="15">
+        <f>VALUE(RIGHT(B4,1))</f>
         <v>5</v>
       </c>
       <c r="H4" s="13">
@@ -1092,14 +1124,17 @@
         <v>5000000000</v>
       </c>
       <c r="I4" s="14">
-        <f>HLOOKUP(E4,$C$22:$E$23,2,FALSE)</f>
+        <f>HLOOKUP(MID(B4,3,1),$B$21:$E$23,3,FALSE)</f>
         <v>50000000</v>
       </c>
-      <c r="J4" s="16">
-        <f>IF(G4&gt;5,H4*0.02,0)</f>
+      <c r="J4" s="16" cm="1">
+        <f t="array" ref="J4">_xlfn.IFS(G4&lt;2,0,G4&lt;=3,1%*H4,G4&gt;3,2%*H4)</f>
         <v>100000000</v>
       </c>
-      <c r="K4" s="13"/>
+      <c r="K4" s="13">
+        <f>H4+I4+J4</f>
+        <v>5150000000</v>
+      </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
@@ -1117,12 +1152,12 @@
         <f t="shared" ref="E5:E8" si="1">HLOOKUP(MID(B5,3,1),$B$21:$E$23,2,FALSE)</f>
         <v>Waskita</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <f t="shared" ref="F5:F8" si="2">VLOOKUP(LEFT(B5,2),$B$15:$D$18,3,FALSE)</f>
         <v>750000000</v>
       </c>
-      <c r="G5" s="15" t="str">
-        <f t="shared" ref="G5:G8" si="3">RIGHT(B5,1)</f>
+      <c r="G5" s="15">
+        <f t="shared" ref="G5:G8" si="3">VALUE(RIGHT(B5,1))</f>
         <v>2</v>
       </c>
       <c r="H5" s="13">
@@ -1130,11 +1165,17 @@
         <v>1500000000</v>
       </c>
       <c r="I5" s="14">
-        <f t="shared" ref="I5:I8" si="5">HLOOKUP(E5,$C$22:$E$23,2,FALSE)</f>
+        <f t="shared" ref="I5:I8" si="5">HLOOKUP(MID(B5,3,1),$B$21:$E$23,3,FALSE)</f>
         <v>45000000</v>
       </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="13"/>
+      <c r="J5" s="16" cm="1">
+        <f t="array" ref="J5">_xlfn.IFS(G5&lt;2,0,G5&lt;=3,1%*H5,G5&gt;3,2%*H5)</f>
+        <v>15000000</v>
+      </c>
+      <c r="K5" s="13">
+        <f t="shared" ref="K5:K8" si="6">H5+I5+J5</f>
+        <v>1560000000</v>
+      </c>
       <c r="L5" s="2"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
@@ -1152,11 +1193,11 @@
         <f t="shared" si="1"/>
         <v>Ciputra</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <f t="shared" si="2"/>
         <v>850000000</v>
       </c>
-      <c r="G6" s="15" t="str">
+      <c r="G6" s="15">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -1168,8 +1209,14 @@
         <f t="shared" si="5"/>
         <v>40000000</v>
       </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="13"/>
+      <c r="J6" s="16" cm="1">
+        <f t="array" ref="J6">_xlfn.IFS(G6&lt;2,0,G6&lt;=3,1%*H6,G6&gt;3,2%*H6)</f>
+        <v>25500000</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="6"/>
+        <v>2615500000</v>
+      </c>
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
@@ -1187,11 +1234,11 @@
         <f t="shared" si="1"/>
         <v>Podomoro</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="13">
         <f t="shared" si="2"/>
         <v>1000000000</v>
       </c>
-      <c r="G7" s="15" t="str">
+      <c r="G7" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -1203,8 +1250,14 @@
         <f t="shared" si="5"/>
         <v>50000000</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="13"/>
+      <c r="J7" s="16" cm="1">
+        <f t="array" ref="J7">_xlfn.IFS(G7&lt;2,0,G7&lt;=3,1%*H7,G7&gt;3,2%*H7)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="13">
+        <f t="shared" si="6"/>
+        <v>1050000000</v>
+      </c>
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
@@ -1222,11 +1275,11 @@
         <f t="shared" si="1"/>
         <v>Waskita</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="13">
         <f t="shared" si="2"/>
         <v>750000000</v>
       </c>
-      <c r="G8" s="15" t="str">
+      <c r="G8" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -1238,8 +1291,14 @@
         <f t="shared" si="5"/>
         <v>45000000</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="13"/>
+      <c r="J8" s="16" cm="1">
+        <f t="array" ref="J8">_xlfn.IFS(G8&lt;2,0,G8&lt;=3,1%*H8,G8&gt;3,2%*H8)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="13">
+        <f t="shared" si="6"/>
+        <v>795000000</v>
+      </c>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
@@ -1248,7 +1307,10 @@
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="27"/>
-      <c r="E9" s="20"/>
+      <c r="E9" s="20">
+        <f>SUM(K4:K8)</f>
+        <v>11170500000</v>
+      </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
       <c r="L9" s="2"/>
@@ -1259,7 +1321,10 @@
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="27"/>
-      <c r="E10" s="20"/>
+      <c r="E10" s="20">
+        <f>MAX(K4:K8)</f>
+        <v>5150000000</v>
+      </c>
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
       <c r="H10" s="21" t="s">
@@ -1278,7 +1343,10 @@
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="27"/>
-      <c r="E11" s="20"/>
+      <c r="E11" s="20">
+        <f>MIN(K4:K8)</f>
+        <v>795000000</v>
+      </c>
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
       <c r="L11" s="2"/>
@@ -1289,7 +1357,10 @@
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="27"/>
-      <c r="E12" s="20"/>
+      <c r="E12" s="20">
+        <f>AVERAGE(K4:K8)</f>
+        <v>2234100000</v>
+      </c>
       <c r="F12" s="20"/>
       <c r="G12" s="20"/>
       <c r="L12" s="2"/>
@@ -1424,7 +1495,7 @@
     <mergeCell ref="F2:F3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J10" r:id="rId1"/>
+    <hyperlink ref="J10" r:id="rId1" xr:uid="{A38C7E0C-6A8B-4E2C-AB0A-B862BC909F0D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
